--- a/input_softitek.xlsx
+++ b/input_softitek.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Local_GIT\Generator_EOB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29ACB1C8-C09E-45C3-B428-0329751C6B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD721308-440A-4879-AD5D-77784BBC1656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="10" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="292">
   <si>
     <t>ta1.1</t>
   </si>
@@ -433,27 +433,15 @@
     <t>tan10</t>
   </si>
   <si>
-    <t>ta11.3</t>
-  </si>
-  <si>
     <t>tan11</t>
   </si>
   <si>
-    <t>ta12.1</t>
-  </si>
-  <si>
     <t>tan12</t>
   </si>
   <si>
-    <t>ta13.2</t>
-  </si>
-  <si>
     <t>tan13</t>
   </si>
   <si>
-    <t>ta14.2</t>
-  </si>
-  <si>
     <t>tan14</t>
   </si>
   <si>
@@ -487,9 +475,6 @@
     <t>tan19</t>
   </si>
   <si>
-    <t>ta20.1</t>
-  </si>
-  <si>
     <t>tan20</t>
   </si>
   <si>
@@ -499,9 +484,6 @@
     <t>tan21</t>
   </si>
   <si>
-    <t>ta22.3</t>
-  </si>
-  <si>
     <t>tan22</t>
   </si>
   <si>
@@ -517,15 +499,9 @@
     <t>ta24.2</t>
   </si>
   <si>
-    <t>ta24.3</t>
-  </si>
-  <si>
     <t>tan24</t>
   </si>
   <si>
-    <t>ta25.1</t>
-  </si>
-  <si>
     <t>tan25</t>
   </si>
   <si>
@@ -538,9 +514,6 @@
     <t>tan26</t>
   </si>
   <si>
-    <t>ta27.1</t>
-  </si>
-  <si>
     <t>ta27.2</t>
   </si>
   <si>
@@ -565,36 +538,6 @@
     <t>tan29</t>
   </si>
   <si>
-    <t>tan30</t>
-  </si>
-  <si>
-    <t>ta30.2</t>
-  </si>
-  <si>
-    <t>ta31.1</t>
-  </si>
-  <si>
-    <t>ta31.2</t>
-  </si>
-  <si>
-    <t>ta31.3</t>
-  </si>
-  <si>
-    <t>tan31</t>
-  </si>
-  <si>
-    <t>ta32.1</t>
-  </si>
-  <si>
-    <t>ta32.2</t>
-  </si>
-  <si>
-    <t>ta32.3</t>
-  </si>
-  <si>
-    <t>tan32</t>
-  </si>
-  <si>
     <t>qfds1</t>
   </si>
   <si>
@@ -926,6 +869,54 @@
   </si>
   <si>
     <t>= QFD/QF state</t>
+  </si>
+  <si>
+    <t>ta9.2</t>
+  </si>
+  <si>
+    <t>ta10.1</t>
+  </si>
+  <si>
+    <t>ta10.3</t>
+  </si>
+  <si>
+    <t>ta11.2</t>
+  </si>
+  <si>
+    <t>ta12.2</t>
+  </si>
+  <si>
+    <t>ta13.3</t>
+  </si>
+  <si>
+    <t>ta14.1</t>
+  </si>
+  <si>
+    <t>ta20.3</t>
+  </si>
+  <si>
+    <t>ta21.1</t>
+  </si>
+  <si>
+    <t>ta21.3</t>
+  </si>
+  <si>
+    <t>ta22.1</t>
+  </si>
+  <si>
+    <t>ta23.2</t>
+  </si>
+  <si>
+    <t>ta25.3</t>
+  </si>
+  <si>
+    <t>ta26.1</t>
+  </si>
+  <si>
+    <t>ta28.1</t>
+  </si>
+  <si>
+    <t>ta28.2</t>
   </si>
 </sst>
 </file>
@@ -1706,7 +1697,7 @@
         <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>108</v>
@@ -2121,6 +2112,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2137,13 +2129,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2451,7 +2443,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>127</v>
+        <v>276</v>
       </c>
       <c r="B26" s="13">
         <f>B18+1</f>
@@ -2464,7 +2456,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B27" s="13">
         <f t="shared" si="1"/>
@@ -2477,7 +2469,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="B28" s="13">
         <f t="shared" si="1"/>
@@ -2490,7 +2482,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B29" s="13">
         <f t="shared" si="1"/>
@@ -2503,7 +2495,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
-        <v>131</v>
+        <v>278</v>
       </c>
       <c r="B30" s="13">
         <f t="shared" si="1"/>
@@ -2516,7 +2508,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B31" s="13">
         <f t="shared" si="1"/>
@@ -2529,7 +2521,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
-        <v>133</v>
+        <v>279</v>
       </c>
       <c r="B32" s="13">
         <f t="shared" si="1"/>
@@ -2542,7 +2534,7 @@
     </row>
     <row r="33" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="28" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B33" s="24">
         <f t="shared" si="1"/>
@@ -2555,7 +2547,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="B34" s="13">
         <f>B26+1</f>
@@ -2568,7 +2560,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B35" s="13">
         <f t="shared" si="1"/>
@@ -2581,7 +2573,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="B36" s="13">
         <f t="shared" si="1"/>
@@ -2594,7 +2586,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B37" s="13">
         <f t="shared" si="1"/>
@@ -2607,7 +2599,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>139</v>
+        <v>282</v>
       </c>
       <c r="B38" s="13">
         <f t="shared" si="1"/>
@@ -2620,7 +2612,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B39" s="13">
         <f t="shared" si="1"/>
@@ -2633,7 +2625,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B40" s="13">
         <f t="shared" si="1"/>
@@ -2646,7 +2638,7 @@
     </row>
     <row r="41" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="30" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B41" s="24">
         <f t="shared" si="1"/>
@@ -2659,7 +2651,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B42" s="13">
         <f>B34+1</f>
@@ -2672,7 +2664,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B43" s="13">
         <f t="shared" si="1"/>
@@ -2685,7 +2677,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B44" s="13">
         <f t="shared" si="1"/>
@@ -2698,7 +2690,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B45" s="13">
         <f t="shared" si="1"/>
@@ -2711,7 +2703,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B46" s="13">
         <f t="shared" si="1"/>
@@ -2724,7 +2716,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B47" s="13">
         <f t="shared" si="1"/>
@@ -2737,7 +2729,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B48" s="13">
         <f t="shared" si="1"/>
@@ -2750,7 +2742,7 @@
     </row>
     <row r="49" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="28" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B49" s="24">
         <f t="shared" si="1"/>
@@ -2763,7 +2755,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="B50" s="13">
         <f>B42+1</f>
@@ -2776,7 +2768,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B51" s="13">
         <f t="shared" si="1"/>
@@ -2789,7 +2781,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>153</v>
+        <v>284</v>
       </c>
       <c r="B52" s="13">
         <f t="shared" si="1"/>
@@ -2802,7 +2794,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B53" s="13">
         <f t="shared" si="1"/>
@@ -2815,7 +2807,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="B54" s="13">
         <f t="shared" si="1"/>
@@ -2828,7 +2820,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="29" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B55" s="13">
         <f t="shared" si="1"/>
@@ -2841,7 +2833,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c r="B56" s="13">
         <f t="shared" si="1"/>
@@ -2854,7 +2846,7 @@
     </row>
     <row r="57" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="30" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B57" s="24">
         <f t="shared" si="1"/>
@@ -2867,7 +2859,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>159</v>
+        <v>287</v>
       </c>
       <c r="B58" s="13">
         <f>B50+1</f>
@@ -2880,7 +2872,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B59" s="13">
         <f t="shared" si="1"/>
@@ -2893,7 +2885,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B60" s="13">
         <f t="shared" si="1"/>
@@ -2906,7 +2898,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B61" s="13">
         <f t="shared" si="1"/>
@@ -2919,7 +2911,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B62" s="13">
         <f t="shared" si="1"/>
@@ -2932,7 +2924,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="29" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B63" s="13">
         <f t="shared" si="1"/>
@@ -2945,7 +2937,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>165</v>
+        <v>288</v>
       </c>
       <c r="B64" s="13">
         <f t="shared" si="1"/>
@@ -2958,7 +2950,7 @@
     </row>
     <row r="65" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="28" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B65" s="24">
         <f t="shared" si="1"/>
@@ -2971,7 +2963,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>167</v>
+        <v>289</v>
       </c>
       <c r="B66" s="13">
         <f>B58+1</f>
@@ -2984,7 +2976,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="29" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="B67" s="13">
         <f t="shared" si="1"/>
@@ -2997,7 +2989,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="B68" s="13">
         <f t="shared" si="1"/>
@@ -3010,7 +3002,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B69" s="13">
         <f t="shared" si="1"/>
@@ -3023,7 +3015,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="B70" s="13">
         <f t="shared" si="1"/>
@@ -3036,7 +3028,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="29" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B71" s="13">
         <f t="shared" si="1"/>
@@ -3049,7 +3041,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="B72" s="13">
         <f t="shared" si="1"/>
@@ -3062,7 +3054,7 @@
     </row>
     <row r="73" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="30" t="s">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="B73" s="24">
         <f t="shared" si="1"/>
@@ -3075,7 +3067,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B74" s="13">
         <f>B66+1</f>
@@ -3088,7 +3080,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="29" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B75" s="13">
         <f t="shared" si="1"/>
@@ -3101,7 +3093,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B76" s="13">
         <f t="shared" ref="B76:B81" si="10">B68+1</f>
@@ -3114,7 +3106,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="29" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B77" s="13">
         <f t="shared" si="10"/>
@@ -3127,7 +3119,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B78" s="13">
         <f t="shared" si="10"/>
@@ -3140,7 +3132,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="29" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B79" s="13">
         <f t="shared" si="10"/>
@@ -3153,7 +3145,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B80" s="13">
         <f t="shared" si="10"/>
@@ -3165,8 +3157,8 @@
       </c>
     </row>
     <row r="81" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="28" t="s">
-        <v>182</v>
+      <c r="A81" s="30" t="s">
+        <v>171</v>
       </c>
       <c r="B81" s="24">
         <f t="shared" si="10"/>
@@ -3178,108 +3170,30 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="B82" s="13">
-        <f>B74+1</f>
-        <v>11</v>
-      </c>
-      <c r="C82" s="6">
-        <f>C74</f>
-        <v>7</v>
-      </c>
+      <c r="B82" s="13"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B83" s="13">
-        <f t="shared" ref="B83:B89" si="12">B75+1</f>
-        <v>11</v>
-      </c>
-      <c r="C83" s="6">
-        <f>C75</f>
-        <v>8</v>
-      </c>
+      <c r="B83" s="13"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B84" s="13">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="C84" s="6">
-        <f t="shared" ref="C84:C89" si="13">C76</f>
-        <v>1</v>
-      </c>
+      <c r="B84" s="13"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B85" s="13">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="C85" s="6">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
+      <c r="B85" s="13"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B86" s="13">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="C86" s="6">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
+      <c r="B86" s="13"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B87" s="13">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="C87" s="6">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
+      <c r="B87" s="13"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B88" s="13">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="C88" s="6">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
+      <c r="B88" s="13"/>
     </row>
     <row r="89" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="B89" s="24">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="C89" s="7">
-        <f t="shared" si="13"/>
-        <v>6</v>
-      </c>
+      <c r="A89" s="30"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="7"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B90" s="13"/>
@@ -3806,18 +3720,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -3828,7 +3742,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
@@ -3839,7 +3753,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
@@ -3850,7 +3764,7 @@
     </row>
     <row r="5" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -3861,7 +3775,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="B6" s="6">
         <f>B2+1</f>
@@ -3874,7 +3788,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="B7" s="6">
         <f t="shared" ref="B7:B29" si="0">B3+1</f>
@@ -3887,7 +3801,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="B8" s="6">
         <f t="shared" si="0"/>
@@ -3900,7 +3814,7 @@
     </row>
     <row r="9" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="B9" s="7">
         <f t="shared" si="0"/>
@@ -3913,7 +3827,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="B10" s="6">
         <f t="shared" si="0"/>
@@ -3926,7 +3840,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="B11" s="6">
         <f t="shared" si="0"/>
@@ -3939,7 +3853,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="B12" s="6">
         <f t="shared" si="0"/>
@@ -3952,7 +3866,7 @@
     </row>
     <row r="13" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="30" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B13" s="7">
         <f t="shared" si="0"/>
@@ -3965,7 +3879,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="B14" s="6">
         <f t="shared" si="0"/>
@@ -3978,7 +3892,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="B15" s="6">
         <f t="shared" si="0"/>
@@ -3991,7 +3905,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="B16" s="6">
         <f t="shared" si="0"/>
@@ -4004,7 +3918,7 @@
     </row>
     <row r="17" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="B17" s="7">
         <f t="shared" si="0"/>
@@ -4017,7 +3931,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="B18" s="6">
         <f t="shared" si="0"/>
@@ -4030,7 +3944,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B19" s="6">
         <f t="shared" si="0"/>
@@ -4043,7 +3957,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="B20" s="6">
         <f t="shared" si="0"/>
@@ -4056,7 +3970,7 @@
     </row>
     <row r="21" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B21" s="7">
         <f t="shared" si="0"/>
@@ -4069,7 +3983,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B22" s="6">
         <f t="shared" si="0"/>
@@ -4082,7 +3996,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B23" s="6">
         <f t="shared" si="0"/>
@@ -4095,7 +4009,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="B24" s="6">
         <f t="shared" si="0"/>
@@ -4108,7 +4022,7 @@
     </row>
     <row r="25" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="B25" s="7">
         <f t="shared" si="0"/>
@@ -4121,7 +4035,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B26" s="6">
         <f>B22+1</f>
@@ -4134,7 +4048,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B27" s="6">
         <f t="shared" si="0"/>
@@ -4147,7 +4061,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B28" s="6">
         <f t="shared" si="0"/>
@@ -4160,7 +4074,7 @@
     </row>
     <row r="29" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B29" s="7">
         <f t="shared" si="0"/>
@@ -4188,19 +4102,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -4224,7 +4138,7 @@
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
@@ -4236,7 +4150,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
@@ -4272,7 +4186,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
@@ -4296,7 +4210,7 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
@@ -4308,7 +4222,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="B11" s="6">
         <v>1</v>
@@ -4332,7 +4246,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B13" s="6">
         <v>1</v>
@@ -4344,7 +4258,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
@@ -4368,7 +4282,7 @@
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B16" s="6">
         <v>1</v>
@@ -4381,7 +4295,7 @@
     </row>
     <row r="17" spans="1:4" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="B17" s="7">
         <v>1</v>
@@ -4407,7 +4321,7 @@
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="B19" s="6">
         <f>B3+1</f>
@@ -4421,7 +4335,7 @@
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="B20" s="6">
         <f t="shared" ref="B20:B33" si="0">B4+1</f>
@@ -4463,7 +4377,7 @@
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="B23" s="6">
         <f t="shared" si="0"/>
@@ -4505,7 +4419,7 @@
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B26" s="6">
         <f t="shared" si="0"/>
@@ -4519,7 +4433,7 @@
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="B27" s="6">
         <f t="shared" si="0"/>
@@ -4533,7 +4447,7 @@
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="B28" s="6">
         <f t="shared" si="0"/>
@@ -4547,7 +4461,7 @@
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B29" s="6">
         <f t="shared" si="0"/>
@@ -4561,7 +4475,7 @@
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="B30" s="6">
         <f t="shared" si="0"/>
@@ -4575,7 +4489,7 @@
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B31" s="6">
         <f t="shared" si="0"/>
@@ -4589,7 +4503,7 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="B32" s="6">
         <f t="shared" si="0"/>
@@ -4603,7 +4517,7 @@
     </row>
     <row r="33" spans="1:4" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B33" s="7">
         <f t="shared" si="0"/>
@@ -4617,7 +4531,7 @@
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B34" s="6">
         <f>B18+1</f>
@@ -4631,7 +4545,7 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B35" s="6">
         <f>B19+1</f>
@@ -4645,7 +4559,7 @@
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B36" s="6">
         <f t="shared" ref="B36:B49" si="2">B20+1</f>
@@ -4659,7 +4573,7 @@
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B37" s="6">
         <f t="shared" si="2"/>
@@ -4673,7 +4587,7 @@
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="B38" s="6">
         <f t="shared" si="2"/>
@@ -4687,7 +4601,7 @@
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="B39" s="6">
         <f t="shared" si="2"/>
@@ -4701,7 +4615,7 @@
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="B40" s="6">
         <f t="shared" si="2"/>
@@ -4715,7 +4629,7 @@
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B41" s="6">
         <f t="shared" si="2"/>
@@ -4729,7 +4643,7 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B42" s="6">
         <f t="shared" si="2"/>
@@ -4743,7 +4657,7 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="B43" s="6">
         <f t="shared" si="2"/>
@@ -4757,7 +4671,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="B44" s="6">
         <f t="shared" si="2"/>
@@ -4771,7 +4685,7 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B45" s="6">
         <f t="shared" si="2"/>
@@ -4785,7 +4699,7 @@
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B46" s="6">
         <f t="shared" si="2"/>
@@ -4799,7 +4713,7 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B47" s="6">
         <f t="shared" si="2"/>
@@ -4813,7 +4727,7 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B48" s="6">
         <f t="shared" si="2"/>
@@ -4827,7 +4741,7 @@
     </row>
     <row r="49" spans="1:4" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="28" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B49" s="7">
         <f t="shared" si="2"/>
@@ -4841,7 +4755,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="B50" s="6">
         <f>B34+1</f>
@@ -4854,7 +4768,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B51" s="6">
         <f>B35+1</f>
@@ -4867,7 +4781,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="B52" s="6">
         <f t="shared" ref="B52:B65" si="4">B36+1</f>
@@ -4880,7 +4794,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="B53" s="6">
         <f t="shared" si="4"/>
@@ -4893,7 +4807,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="B54" s="6">
         <f t="shared" si="4"/>
@@ -4906,7 +4820,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="29" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="B55" s="6">
         <f t="shared" si="4"/>
@@ -4919,7 +4833,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="B56" s="6">
         <f t="shared" si="4"/>
@@ -4932,7 +4846,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="29" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="B57" s="6">
         <f t="shared" si="4"/>
@@ -4945,7 +4859,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="B58" s="6">
         <f t="shared" si="4"/>
@@ -4958,7 +4872,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="B59" s="6">
         <f t="shared" si="4"/>
@@ -4971,7 +4885,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="B60" s="6">
         <f t="shared" si="4"/>
@@ -4984,7 +4898,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B61" s="6">
         <f t="shared" si="4"/>
@@ -4997,7 +4911,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="B62" s="6">
         <f t="shared" si="4"/>
@@ -5010,7 +4924,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="29" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="B63" s="6">
         <f t="shared" si="4"/>
@@ -5023,7 +4937,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="B64" s="6">
         <f t="shared" si="4"/>
@@ -5036,7 +4950,7 @@
     </row>
     <row r="65" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="30" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="B65" s="7">
         <f t="shared" si="4"/>
@@ -5049,7 +4963,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="B66" s="6">
         <f>B50+1</f>
@@ -5062,7 +4976,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="29" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B67" s="6">
         <f>B51+1</f>
@@ -5075,7 +4989,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B68" s="6">
         <f t="shared" ref="B68:B81" si="6">B52+1</f>
@@ -5088,7 +5002,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="B69" s="6">
         <f t="shared" si="6"/>
@@ -5101,7 +5015,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B70" s="6">
         <f t="shared" si="6"/>
@@ -5114,7 +5028,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="29" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="B71" s="6">
         <f t="shared" si="6"/>
@@ -5127,7 +5041,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="B72" s="6">
         <f t="shared" si="6"/>
@@ -5140,7 +5054,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="29" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="B73" s="6">
         <f t="shared" si="6"/>
@@ -5153,7 +5067,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B74" s="6">
         <f t="shared" si="6"/>
@@ -5166,7 +5080,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="29" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="B75" s="6">
         <f t="shared" si="6"/>
@@ -5179,7 +5093,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B76" s="6">
         <f t="shared" si="6"/>
@@ -5192,7 +5106,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="29" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B77" s="6">
         <f t="shared" si="6"/>
@@ -5205,7 +5119,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="B78" s="6">
         <f t="shared" si="6"/>
@@ -5218,7 +5132,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="29" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="B79" s="6">
         <f t="shared" si="6"/>
@@ -5231,7 +5145,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B80" s="6">
         <f t="shared" si="6"/>
@@ -5244,7 +5158,7 @@
     </row>
     <row r="81" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="30" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="B81" s="7">
         <f t="shared" si="6"/>
@@ -5257,7 +5171,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="B82" s="6">
         <f>B66+1</f>
@@ -5270,7 +5184,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="29" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="B83" s="6">
         <f>B67+1</f>
@@ -5283,7 +5197,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B84" s="6">
         <f t="shared" ref="B84:B97" si="8">B68+1</f>
@@ -5296,7 +5210,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="29" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="B85" s="6">
         <f t="shared" si="8"/>
@@ -5309,7 +5223,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="B86" s="6">
         <f t="shared" si="8"/>
@@ -5322,7 +5236,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="29" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="B87" s="6">
         <f t="shared" si="8"/>
@@ -5335,7 +5249,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B88" s="6">
         <f t="shared" si="8"/>
@@ -5348,7 +5262,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="29" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="B89" s="6">
         <f t="shared" si="8"/>
@@ -5361,7 +5275,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="B90" s="6">
         <f t="shared" si="8"/>
@@ -5374,7 +5288,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="29" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="B91" s="6">
         <f t="shared" si="8"/>
@@ -5387,7 +5301,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="38" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="B92" s="6">
         <f t="shared" si="8"/>
@@ -5413,7 +5327,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B94" s="6">
         <f t="shared" si="8"/>
@@ -5426,7 +5340,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B95" s="6">
         <f t="shared" si="8"/>
@@ -5439,7 +5353,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B96" s="6">
         <f t="shared" si="8"/>
@@ -5452,7 +5366,7 @@
     </row>
     <row r="97" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B97" s="7">
         <f t="shared" si="8"/>
@@ -5465,7 +5379,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B98" s="6">
         <f>B82+1</f>
@@ -5478,7 +5392,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B99" s="6">
         <f>B83+1</f>
@@ -5491,7 +5405,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B100" s="6">
         <f t="shared" ref="B100:B113" si="10">B84+1</f>
@@ -5504,7 +5418,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B101" s="6">
         <f t="shared" si="10"/>
@@ -5517,7 +5431,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B102" s="6">
         <f t="shared" si="10"/>
@@ -5530,7 +5444,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B103" s="6">
         <f t="shared" si="10"/>
@@ -5543,7 +5457,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B104" s="6">
         <f t="shared" si="10"/>
@@ -5556,7 +5470,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B105" s="6">
         <f t="shared" si="10"/>
@@ -5569,7 +5483,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B106" s="6">
         <f t="shared" si="10"/>
@@ -5582,7 +5496,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B107" s="6">
         <f t="shared" si="10"/>
@@ -5595,7 +5509,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B108" s="6">
         <f t="shared" si="10"/>
@@ -5608,7 +5522,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B109" s="6">
         <f t="shared" si="10"/>
@@ -5621,7 +5535,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B110" s="6">
         <f t="shared" si="10"/>
@@ -5634,7 +5548,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B111" s="6">
         <f t="shared" si="10"/>
@@ -5647,7 +5561,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B112" s="6">
         <f t="shared" si="10"/>
@@ -5660,7 +5574,7 @@
     </row>
     <row r="113" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B113" s="7">
         <f t="shared" si="10"/>
@@ -5687,18 +5601,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -5720,7 +5634,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
@@ -5731,7 +5645,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
@@ -5742,7 +5656,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -5753,7 +5667,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
@@ -5786,7 +5700,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
@@ -5797,7 +5711,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B11" s="6">
         <v>1</v>
@@ -5808,7 +5722,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="B12" s="6">
         <v>1</v>
@@ -5819,7 +5733,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B13" s="6">
         <v>1</v>
@@ -5830,7 +5744,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
@@ -5841,7 +5755,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B15" s="6">
         <v>1</v>
@@ -5852,7 +5766,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="B16" s="6">
         <v>1</v>
@@ -5863,7 +5777,7 @@
     </row>
     <row r="17" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="B17" s="7">
         <v>1</v>
@@ -5874,7 +5788,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B18" s="6">
         <f>B2+1</f>
@@ -5887,7 +5801,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B19" s="6">
         <f>B3+1</f>
@@ -5900,7 +5814,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="B20" s="6">
         <f t="shared" ref="B20:B33" si="0">B4+1</f>
@@ -5913,7 +5827,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="B21" s="6">
         <f t="shared" si="0"/>
@@ -5926,7 +5840,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="B22" s="6">
         <f t="shared" si="0"/>
@@ -5939,7 +5853,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B23" s="6">
         <f t="shared" si="0"/>
@@ -5952,7 +5866,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="B24" s="6">
         <f t="shared" si="0"/>
@@ -5965,7 +5879,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B25" s="6">
         <f t="shared" si="0"/>
@@ -5978,7 +5892,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B26" s="6">
         <f t="shared" si="0"/>
@@ -5991,7 +5905,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="B27" s="6">
         <f t="shared" si="0"/>
@@ -6004,7 +5918,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B28" s="6">
         <f t="shared" si="0"/>
@@ -6017,7 +5931,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="B29" s="6">
         <f t="shared" si="0"/>
@@ -6030,7 +5944,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="B30" s="6">
         <f t="shared" si="0"/>
@@ -6043,7 +5957,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="B31" s="6">
         <f t="shared" si="0"/>
@@ -6056,7 +5970,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B32" s="6">
         <f t="shared" si="0"/>
@@ -6069,7 +5983,7 @@
     </row>
     <row r="33" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="B33" s="7">
         <f t="shared" si="0"/>
@@ -6108,7 +6022,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B36" s="6">
         <f t="shared" ref="B36:B49" si="2">B20+1</f>
@@ -6121,7 +6035,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B37" s="6">
         <f t="shared" si="2"/>
@@ -6134,7 +6048,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B38" s="6">
         <f t="shared" si="2"/>
@@ -6147,7 +6061,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B39" s="6">
         <f t="shared" si="2"/>
@@ -6160,7 +6074,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B40" s="6">
         <f t="shared" si="2"/>
@@ -6173,7 +6087,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B41" s="6">
         <f t="shared" si="2"/>
@@ -6186,7 +6100,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B42" s="6">
         <f t="shared" si="2"/>
@@ -6199,7 +6113,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B43" s="6">
         <f t="shared" si="2"/>
@@ -6212,7 +6126,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B44" s="6">
         <f t="shared" si="2"/>
@@ -6225,7 +6139,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B45" s="6">
         <f t="shared" si="2"/>
@@ -6238,7 +6152,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B46" s="6">
         <f t="shared" si="2"/>
@@ -6251,7 +6165,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B47" s="6">
         <f t="shared" si="2"/>
@@ -6264,7 +6178,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B48" s="6">
         <f t="shared" si="2"/>
@@ -6277,7 +6191,7 @@
     </row>
     <row r="49" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B49" s="7">
         <f t="shared" si="2"/>

--- a/input_softitek.xlsx
+++ b/input_softitek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Local_GIT\Generator_EOB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Generator1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD721308-440A-4879-AD5D-77784BBC1656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB6BBC0-024C-453B-95DE-B4E50A6FBB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="10" r:id="rId1"/>
@@ -1142,6 +1142,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1149,12 +1155,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1592,17 +1592,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>6</v>
@@ -1817,11 +1817,11 @@
       <c r="B1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -1830,9 +1830,9 @@
       <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
@@ -1841,9 +1841,9 @@
       <c r="B3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1852,9 +1852,9 @@
       <c r="B4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -1863,9 +1863,9 @@
       <c r="B5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -1874,9 +1874,9 @@
       <c r="B6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
@@ -1885,9 +1885,9 @@
       <c r="B7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -1896,9 +1896,9 @@
       <c r="B8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -1907,9 +1907,9 @@
       <c r="B9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
@@ -1918,9 +1918,9 @@
       <c r="B10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
@@ -3578,53 +3578,53 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="27"/>
-      <c r="B209" s="42"/>
+      <c r="B209" s="39"/>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B210" s="42"/>
+      <c r="B210" s="39"/>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="42"/>
+      <c r="B211" s="39"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="42"/>
+      <c r="B212" s="39"/>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B213" s="42"/>
+      <c r="B213" s="39"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B214" s="42"/>
+      <c r="B214" s="39"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B215" s="42"/>
+      <c r="B215" s="39"/>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B216" s="42"/>
+      <c r="B216" s="39"/>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B217" s="42"/>
+      <c r="B217" s="39"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B218" s="42"/>
+      <c r="B218" s="39"/>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B219" s="42"/>
+      <c r="B219" s="39"/>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B220" s="42"/>
+      <c r="B220" s="39"/>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B221" s="42"/>
+      <c r="B221" s="39"/>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B222" s="42"/>
+      <c r="B222" s="39"/>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B223" s="42"/>
+      <c r="B223" s="39"/>
     </row>
     <row r="224" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="30"/>
-      <c r="B224" s="43"/>
+      <c r="B224" s="40"/>
       <c r="C224" s="7"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">

--- a/input_softitek.xlsx
+++ b/input_softitek.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Generator1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB6BBC0-024C-453B-95DE-B4E50A6FBB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C94AA7-4FDE-4050-B296-28FF3E82B4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="10" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="293">
   <si>
     <t>ta1.1</t>
   </si>
@@ -917,6 +917,9 @@
   </si>
   <si>
     <t>ta28.2</t>
+  </si>
+  <si>
+    <t>alDt</t>
   </si>
 </sst>
 </file>
@@ -1142,12 +1145,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1155,6 +1152,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1592,11 +1595,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
@@ -1817,11 +1820,11 @@
       <c r="B1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -1830,9 +1833,9 @@
       <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
@@ -1841,9 +1844,9 @@
       <c r="B3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1852,9 +1855,9 @@
       <c r="B4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -1863,9 +1866,9 @@
       <c r="B5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -1874,9 +1877,9 @@
       <c r="B6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
@@ -1885,9 +1888,9 @@
       <c r="B7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -1896,9 +1899,9 @@
       <c r="B8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -1907,9 +1910,9 @@
       <c r="B9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
@@ -1918,9 +1921,9 @@
       <c r="B10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
@@ -3578,53 +3581,53 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="27"/>
-      <c r="B209" s="39"/>
+      <c r="B209" s="42"/>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B210" s="39"/>
+      <c r="B210" s="42"/>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="39"/>
+      <c r="B211" s="42"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="39"/>
+      <c r="B212" s="42"/>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B213" s="39"/>
+      <c r="B213" s="42"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B214" s="39"/>
+      <c r="B214" s="42"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B215" s="39"/>
+      <c r="B215" s="42"/>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B216" s="39"/>
+      <c r="B216" s="42"/>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B217" s="39"/>
+      <c r="B217" s="42"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B218" s="39"/>
+      <c r="B218" s="42"/>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B219" s="39"/>
+      <c r="B219" s="42"/>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B220" s="39"/>
+      <c r="B220" s="42"/>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B221" s="39"/>
+      <c r="B221" s="42"/>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B222" s="39"/>
+      <c r="B222" s="42"/>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B223" s="39"/>
+      <c r="B223" s="42"/>
     </row>
     <row r="224" spans="1:3" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="30"/>
-      <c r="B224" s="40"/>
+      <c r="B224" s="43"/>
       <c r="C224" s="7"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -6022,7 +6025,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>171</v>
+        <v>292</v>
       </c>
       <c r="B36" s="6">
         <f t="shared" ref="B36:B49" si="2">B20+1</f>
